--- a/data/trans_orig/P79A5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A5_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21131</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19773</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>870</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1609,17 +1609,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>61709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
